--- a/data/trans_dic/LAWTONB_2R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R3-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia moderada o superior</t>
+          <t>Población con dependencia moderada o superior (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 14,99</t>
+          <t>1,55; 14,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 29,24</t>
+          <t>2,5; 28,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 14,91</t>
+          <t>2,18; 16,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 8,93</t>
+          <t>2,35; 8,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,8; 39,18</t>
+          <t>7,42; 41,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,15</t>
+          <t>0,0; 26,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 29,49</t>
+          <t>3,53; 28,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 19,54</t>
+          <t>6,15; 19,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,52; 19,02</t>
+          <t>5,76; 19,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 23,55</t>
+          <t>4,28; 22,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 16,31</t>
+          <t>4,09; 15,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 10,97</t>
+          <t>4,72; 11,47</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 26,82</t>
+          <t>3,84; 25,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 25,7</t>
+          <t>5,24; 24,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,6; 24,3</t>
+          <t>6,57; 25,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,37; 16,88</t>
+          <t>5,95; 16,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,69; 47,35</t>
+          <t>5,59; 47,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 47,01</t>
+          <t>5,9; 44,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,34; 51,52</t>
+          <t>6,06; 47,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,0; 22,12</t>
+          <t>8,18; 22,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 24,96</t>
+          <t>6,04; 25,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 25,64</t>
+          <t>7,63; 25,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,45; 26,1</t>
+          <t>8,2; 25,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,54; 16,7</t>
+          <t>8,31; 17,06</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 18,86</t>
+          <t>4,97; 19,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,0; 23,68</t>
+          <t>9,29; 24,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,96; 16,86</t>
+          <t>6,37; 17,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 20,49</t>
+          <t>9,88; 21,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,73; 40,0</t>
+          <t>4,72; 40,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,46; 36,11</t>
+          <t>13,08; 36,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,92; 35,8</t>
+          <t>9,75; 39,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,62; 37,27</t>
+          <t>19,42; 36,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 20,25</t>
+          <t>7,67; 21,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,9; 24,16</t>
+          <t>11,88; 25,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 20,23</t>
+          <t>8,51; 19,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,41; 24,06</t>
+          <t>14,84; 24,13</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,39; 19,91</t>
+          <t>11,43; 19,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,33; 33,95</t>
+          <t>20,96; 33,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,88; 20,71</t>
+          <t>10,98; 19,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,55; 26,67</t>
+          <t>17,47; 26,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,6; 24,77</t>
+          <t>8,79; 25,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,62; 37,57</t>
+          <t>14,47; 36,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,76; 30,48</t>
+          <t>12,47; 32,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 19,57</t>
+          <t>1,74; 19,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,76; 19,27</t>
+          <t>11,59; 19,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,25; 32,5</t>
+          <t>21,89; 32,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,78; 21,69</t>
+          <t>12,36; 20,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 21,64</t>
+          <t>4,74; 21,78</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,34; 23,0</t>
+          <t>5,17; 22,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,52; 31,71</t>
+          <t>15,07; 31,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,17; 31,01</t>
+          <t>17,4; 31,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,62; 30,53</t>
+          <t>16,71; 29,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,62; 36,39</t>
+          <t>17,57; 36,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,96; 41,46</t>
+          <t>26,78; 40,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,89; 32,8</t>
+          <t>17,79; 33,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,71; 38,89</t>
+          <t>29,86; 38,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,44; 28,37</t>
+          <t>14,78; 28,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,29; 34,73</t>
+          <t>24,71; 35,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19,8; 29,4</t>
+          <t>19,51; 29,4</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,1; 34,5</t>
+          <t>27,24; 34,8</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 75,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30,83; 100,0</t>
+          <t>16,47; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,87; 21,4</t>
+          <t>13,93; 21,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,33; 29,38</t>
+          <t>19,65; 28,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,6; 29,82</t>
+          <t>20,28; 29,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,03; 37,99</t>
+          <t>30,25; 38,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,98; 21,5</t>
+          <t>13,99; 21,33</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,48; 28,74</t>
+          <t>19,68; 28,37</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20,6; 29,82</t>
+          <t>20,28; 29,79</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30,34; 38,08</t>
+          <t>30,52; 38,41</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,01; 15,81</t>
+          <t>10,28; 16,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,15; 24,86</t>
+          <t>17,41; 24,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,58; 17,89</t>
+          <t>12,23; 17,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,45; 18,74</t>
+          <t>14,34; 19,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,58; 21,8</t>
+          <t>15,61; 21,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,86; 29,6</t>
+          <t>22,95; 29,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,13; 26,84</t>
+          <t>20,37; 26,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,63; 29,1</t>
+          <t>11,49; 29,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,15; 18,38</t>
+          <t>14,42; 18,41</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,45; 26,37</t>
+          <t>21,65; 26,38</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,62; 22,2</t>
+          <t>17,42; 22,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,31; 23,77</t>
+          <t>12,68; 23,69</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia moderada o superior</t>
+          <t>Población con dependencia moderada o superior (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>965; 8959</t>
+          <t>929; 8851</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1896; 12841</t>
+          <t>1097; 12634</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1481; 10236</t>
+          <t>1498; 11533</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2680; 9506</t>
+          <t>2502; 8917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2614; 11639</t>
+          <t>2205; 12235</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6867</t>
+          <t>0; 6777</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1225; 10877</t>
+          <t>1302; 10596</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4222; 12766</t>
+          <t>4018; 12937</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4936; 17018</t>
+          <t>5153; 17158</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3119; 16298</t>
+          <t>2962; 15279</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3868; 17213</t>
+          <t>4316; 15995</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7871; 18843</t>
+          <t>8105; 19704</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2542; 13632</t>
+          <t>1954; 12990</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3069; 15582</t>
+          <t>3179; 14752</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2988; 12962</t>
+          <t>3504; 13507</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6055; 16035</t>
+          <t>5652; 15701</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>899; 7474</t>
+          <t>882; 7428</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1068; 8885</t>
+          <t>1115; 8401</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1114; 9062</t>
+          <t>1065; 8438</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3756; 10381</t>
+          <t>3839; 10673</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4279; 16628</t>
+          <t>4024; 17157</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5971; 20394</t>
+          <t>6072; 20526</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5991; 18512</t>
+          <t>5819; 18188</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12119; 23709</t>
+          <t>11794; 24209</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3451; 13536</t>
+          <t>3565; 14000</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10674; 28096</t>
+          <t>11028; 28741</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7166; 20281</t>
+          <t>7664; 21637</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10217; 20795</t>
+          <t>10032; 21354</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1149; 9711</t>
+          <t>1146; 9818</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7350; 19722</t>
+          <t>7143; 19861</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4582; 16542</t>
+          <t>4507; 18034</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10155; 19294</t>
+          <t>10053; 18980</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6970; 19442</t>
+          <t>7366; 20706</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20617; 41866</t>
+          <t>20579; 43807</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15172; 33682</t>
+          <t>14160; 32569</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22090; 36871</t>
+          <t>22738; 36973</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29621; 51787</t>
+          <t>29732; 51430</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49427; 78672</t>
+          <t>48579; 77096</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22188; 42216</t>
+          <t>22392; 40618</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41382; 62863</t>
+          <t>41194; 61786</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7372; 21238</t>
+          <t>7541; 21452</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8787; 22578</t>
+          <t>8697; 22016</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12635; 30185</t>
+          <t>12349; 32113</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5002; 63928</t>
+          <t>5671; 65278</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40675; 66626</t>
+          <t>40088; 65783</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64928; 94853</t>
+          <t>63875; 93872</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38718; 65713</t>
+          <t>37426; 63146</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26959; 121684</t>
+          <t>26671; 122519</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2963; 12758</t>
+          <t>2866; 12486</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14906; 32569</t>
+          <t>15478; 32194</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24933; 45029</t>
+          <t>25267; 45104</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15030; 27608</t>
+          <t>15112; 26891</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15992; 35022</t>
+          <t>16913; 34824</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50798; 78108</t>
+          <t>50460; 76759</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28538; 52334</t>
+          <t>28379; 52920</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>60438; 79111</t>
+          <t>60736; 79073</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21909; 43039</t>
+          <t>22428; 43181</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70702; 101086</t>
+          <t>71934; 102783</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60334; 89587</t>
+          <t>59470; 89598</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>79645; 101363</t>
+          <t>80031; 102249</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3645</t>
+          <t>0; 2760</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1132</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>988; 3204</t>
+          <t>528; 3204</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58948; 90965</t>
+          <t>59192; 91642</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>80250; 115973</t>
+          <t>77576; 114280</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>85087; 123167</t>
+          <t>83781; 123067</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>96044; 121523</t>
+          <t>96765; 122452</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>59939; 92167</t>
+          <t>59976; 91446</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>77291; 114003</t>
+          <t>78081; 112529</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>85087; 123167</t>
+          <t>83781; 123067</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>98028; 123031</t>
+          <t>98595; 124074</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>50193; 79275</t>
+          <t>51582; 80511</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>95990; 139114</t>
+          <t>97438; 137651</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74368; 105805</t>
+          <t>72292; 106074</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91358; 118485</t>
+          <t>90646; 120451</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>105422; 147546</t>
+          <t>105642; 146624</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>169629; 219663</t>
+          <t>170290; 218684</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>155502; 207338</t>
+          <t>157358; 207800</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>128108; 295095</t>
+          <t>116527; 294119</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>166698; 216580</t>
+          <t>169867; 216907</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>279181; 343255</t>
+          <t>281848; 343437</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>240226; 302743</t>
+          <t>237596; 304012</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>219185; 391379</t>
+          <t>208826; 390068</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/LAWTONB_2R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R3-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 14,81</t>
+          <t>1,57; 14,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 28,77</t>
+          <t>2,53; 28,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 16,8</t>
+          <t>1,33; 13,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,38</t>
+          <t>2,27; 8,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,42; 41,18</t>
+          <t>7,38; 39,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,8</t>
+          <t>0,0; 26,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 28,72</t>
+          <t>3,47; 29,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 19,81</t>
+          <t>5,92; 20,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 19,17</t>
+          <t>5,54; 19,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 22,08</t>
+          <t>4,44; 21,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 15,16</t>
+          <t>3,81; 15,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 11,47</t>
+          <t>4,66; 11,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 25,56</t>
+          <t>4,13; 27,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 24,33</t>
+          <t>5,21; 25,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,57; 25,32</t>
+          <t>6,63; 25,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 16,53</t>
+          <t>6,44; 16,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 47,06</t>
+          <t>5,74; 48,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,9; 44,45</t>
+          <t>5,74; 47,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 47,97</t>
+          <t>6,41; 49,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,18; 22,74</t>
+          <t>8,58; 23,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,04; 25,75</t>
+          <t>5,89; 24,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,63; 25,81</t>
+          <t>7,75; 26,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,2; 25,64</t>
+          <t>8,06; 25,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,31; 17,06</t>
+          <t>8,23; 16,54</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 19,51</t>
+          <t>5,07; 18,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,29; 24,22</t>
+          <t>8,42; 24,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 17,99</t>
+          <t>6,31; 17,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,88; 21,04</t>
+          <t>9,12; 19,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 40,45</t>
+          <t>4,78; 40,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,08; 36,36</t>
+          <t>13,07; 36,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,75; 39,03</t>
+          <t>8,42; 38,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,42; 36,66</t>
+          <t>20,59; 39,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,67; 21,56</t>
+          <t>7,58; 20,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,88; 25,28</t>
+          <t>11,81; 24,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,51; 19,56</t>
+          <t>9,4; 19,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,84; 24,13</t>
+          <t>14,54; 24,11</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,43; 19,78</t>
+          <t>11,22; 19,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,96; 33,27</t>
+          <t>21,49; 34,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,98; 19,92</t>
+          <t>10,77; 20,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,47; 26,21</t>
+          <t>17,08; 26,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,79; 25,02</t>
+          <t>8,91; 24,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,47; 36,64</t>
+          <t>14,62; 37,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,47; 32,42</t>
+          <t>12,56; 31,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 19,98</t>
+          <t>14,41; 23,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,59; 19,02</t>
+          <t>11,67; 18,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,89; 32,16</t>
+          <t>21,16; 32,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,36; 20,85</t>
+          <t>12,48; 21,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 21,78</t>
+          <t>17,58; 24,41</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 22,51</t>
+          <t>5,52; 22,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,07; 31,35</t>
+          <t>13,61; 30,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,4; 31,06</t>
+          <t>17,38; 31,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,71; 29,74</t>
+          <t>15,95; 28,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,57; 36,18</t>
+          <t>17,25; 35,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,78; 40,74</t>
+          <t>26,98; 41,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,79; 33,17</t>
+          <t>17,38; 32,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,86; 38,87</t>
+          <t>29,96; 38,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,78; 28,46</t>
+          <t>14,14; 27,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,71; 35,31</t>
+          <t>24,22; 35,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19,51; 29,4</t>
+          <t>19,07; 29,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,24; 34,8</t>
+          <t>26,54; 34,17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,71</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,47; 100,0</t>
+          <t>18,92; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,93; 21,56</t>
+          <t>13,94; 21,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,65; 28,95</t>
+          <t>20,08; 29,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,28; 29,79</t>
+          <t>20,57; 30,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,25; 38,28</t>
+          <t>30,32; 37,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,99; 21,33</t>
+          <t>14,1; 21,96</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,68; 28,37</t>
+          <t>19,97; 28,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20,28; 29,79</t>
+          <t>20,57; 30,07</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30,52; 38,41</t>
+          <t>30,94; 38,73</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,28; 16,05</t>
+          <t>10,29; 15,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,41; 24,6</t>
+          <t>17,04; 24,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,23; 17,94</t>
+          <t>12,53; 17,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,34; 19,05</t>
+          <t>13,89; 18,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,61; 21,66</t>
+          <t>15,63; 21,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,95; 29,47</t>
+          <t>22,66; 29,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,37; 26,9</t>
+          <t>20,04; 26,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,49; 29,01</t>
+          <t>26,3; 30,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,42; 18,41</t>
+          <t>14,13; 18,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,65; 26,38</t>
+          <t>21,22; 26,21</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,42; 22,29</t>
+          <t>17,72; 22,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,68; 23,69</t>
+          <t>21,37; 24,65</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7610</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>13837</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>929; 8851</t>
+          <t>939; 8860</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1097; 12634</t>
+          <t>1112; 12557</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1498; 11533</t>
+          <t>915; 9544</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2502; 8917</t>
+          <t>2709; 9990</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2205; 12235</t>
+          <t>2192; 11880</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6777</t>
+          <t>0; 6751</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1302; 10596</t>
+          <t>1278; 11049</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4018; 12937</t>
+          <t>4411; 15078</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5153; 17158</t>
+          <t>4956; 17344</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2962; 15279</t>
+          <t>3070; 15222</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4316; 15995</t>
+          <t>4024; 16596</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8105; 19704</t>
+          <t>9030; 21499</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>8053</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16946</t>
+          <t>19112</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1954; 12990</t>
+          <t>2101; 13762</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3179; 14752</t>
+          <t>3159; 15364</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3504; 13507</t>
+          <t>3537; 13398</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5652; 15701</t>
+          <t>6745; 17148</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>882; 7428</t>
+          <t>905; 7632</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1115; 8401</t>
+          <t>1085; 8933</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1065; 8438</t>
+          <t>1127; 8768</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3839; 10673</t>
+          <t>4753; 13188</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4024; 17157</t>
+          <t>3926; 16429</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6072; 20526</t>
+          <t>6164; 20772</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5819; 18188</t>
+          <t>5718; 17916</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11794; 24209</t>
+          <t>13176; 26475</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14843</t>
+          <t>15028</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>16723</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29188</t>
+          <t>31751</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3565; 14000</t>
+          <t>3640; 13321</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11028; 28741</t>
+          <t>9991; 28700</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7664; 21637</t>
+          <t>7591; 20691</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10032; 21354</t>
+          <t>10207; 21446</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1146; 9818</t>
+          <t>1161; 9783</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7143; 19861</t>
+          <t>7140; 19897</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4507; 18034</t>
+          <t>3891; 17790</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10053; 18980</t>
+          <t>11720; 22374</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7366; 20706</t>
+          <t>7284; 19621</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20579; 43807</t>
+          <t>20458; 43102</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14160; 32569</t>
+          <t>15641; 32923</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22738; 36973</t>
+          <t>24545; 40699</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51695</t>
+          <t>55097</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22653</t>
+          <t>24934</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74347</t>
+          <t>80031</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29732; 51430</t>
+          <t>29180; 51111</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48579; 77096</t>
+          <t>49794; 78935</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22392; 40618</t>
+          <t>21950; 41257</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41194; 61786</t>
+          <t>43949; 67256</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7541; 21452</t>
+          <t>7640; 21196</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8697; 22016</t>
+          <t>8785; 22511</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12349; 32113</t>
+          <t>12439; 31473</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5671; 65278</t>
+          <t>18860; 31223</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40088; 65783</t>
+          <t>40368; 64712</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63875; 93872</t>
+          <t>61759; 95023</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37426; 63146</t>
+          <t>37790; 64102</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26671; 122519</t>
+          <t>68238; 94779</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>21725</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>69783</t>
+          <t>74978</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>96703</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2866; 12486</t>
+          <t>3064; 12236</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15478; 32194</t>
+          <t>13972; 31372</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25267; 45104</t>
+          <t>25233; 45458</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15112; 26891</t>
+          <t>15794; 28522</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16913; 34824</t>
+          <t>16607; 34238</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50460; 76759</t>
+          <t>50833; 78608</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28379; 52920</t>
+          <t>27723; 51217</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>60736; 79073</t>
+          <t>65397; 84973</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22428; 43181</t>
+          <t>21454; 41342</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71934; 102783</t>
+          <t>70496; 103428</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59470; 89598</t>
+          <t>58123; 88783</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>80031; 102249</t>
+          <t>84224; 108434</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>108779</t>
+          <t>117371</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>110924</t>
+          <t>119575</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2760</t>
+          <t>0; 3645</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>528; 3204</t>
+          <t>620; 3276</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>59192; 91642</t>
+          <t>59259; 91117</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>77576; 114280</t>
+          <t>79265; 115245</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>83781; 123067</t>
+          <t>84972; 124211</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>96765; 122452</t>
+          <t>104196; 129775</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>59976; 91446</t>
+          <t>60433; 94146</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>78081; 112529</t>
+          <t>79209; 114188</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>83781; 123067</t>
+          <t>84972; 124211</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>98595; 124074</t>
+          <t>107330; 134386</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104444</t>
+          <t>110691</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>229865</t>
+          <t>250317</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>334309</t>
+          <t>361008</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>51582; 80511</t>
+          <t>51605; 79900</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>97438; 137651</t>
+          <t>95353; 138893</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>72292; 106074</t>
+          <t>74075; 106225</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>90646; 120451</t>
+          <t>96594; 127590</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>105642; 146624</t>
+          <t>105823; 147711</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>170290; 218684</t>
+          <t>168159; 218593</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>157358; 207800</t>
+          <t>154751; 206245</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>116527; 294119</t>
+          <t>231330; 270621</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>169867; 216907</t>
+          <t>166564; 217279</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>281848; 343437</t>
+          <t>276183; 341217</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>237596; 304012</t>
+          <t>241668; 300718</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>208826; 390068</t>
+          <t>336657; 388253</t>
         </is>
       </c>
     </row>
